--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-immunization.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T10:23:38+00:00</t>
+    <t>2025-02-24T13:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-immunization.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-immunization.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:55:23+00:00</t>
+    <t>2025-02-26T08:56:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-immunization.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T08:56:44+00:00</t>
+    <t>2025-03-04T11:06:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-immunization.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T11:06:18+00:00</t>
+    <t>2025-03-06T12:24:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-immunization.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T12:24:43+00:00</t>
+    <t>2025-03-20T12:28:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-immunization.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-20T12:28:15+00:00</t>
+    <t>2025-03-24T06:28:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-immunization.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-immunization.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-immunization</t>
+    <t>https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-immunization</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T06:28:05+00:00</t>
+    <t>2025-03-24T07:27:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -455,7 +455,7 @@
     <t>basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/immunization-basedOn}
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/elga/aps/r4/StructureDefinition/immunization-basedOn}
 </t>
   </si>
   <si>
@@ -590,7 +590,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga-austrianpatientsummary-r4/ValueSet/at-aps-immunization-vaccine-codes</t>
+    <t>https://fhir.hl7.at/elga/aps/r4/ValueSet/at-aps-immunization-vaccine-codes</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -611,7 +611,7 @@
     <t>Immunization.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-patient)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient)
 </t>
   </si>
   <si>
@@ -1665,7 +1665,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="98.91015625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="79.3828125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1680,7 +1680,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="66.7265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="89.06640625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="69.5390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-immunization.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T07:27:46+00:00</t>
+    <t>2025-03-24T07:43:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-immunization.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-18T10:23:29+00:00</t>
+    <t>2026-01-28T10:05:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -859,7 +859,7 @@
     <t>Immunization.manufacturer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-organization)
 </t>
   </si>
   <si>
@@ -1054,7 +1054,7 @@
     <t>Immunization.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitioner|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitionerrole|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-organization)
 </t>
   </si>
   <si>
@@ -1122,7 +1122,7 @@
     <t>Immunization.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-condition|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-observation|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-diagnosticreport)
 </t>
   </si>
   <si>
@@ -1307,7 +1307,7 @@
     <t>Immunization.reaction.detail</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-observation)
 </t>
   </si>
   <si>
@@ -1731,7 +1731,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="158.578125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="174.80859375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-immunization.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T10:05:57+00:00</t>
+    <t>2026-01-29T06:33:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-immunization.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T06:33:09+00:00</t>
+    <t>2026-02-03T10:06:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-immunization.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T10:06:44+00:00</t>
+    <t>2026-02-03T10:34:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-immunization.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T10:34:36+00:00</t>
+    <t>2026-02-09T07:50:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-immunization.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T07:50:08+00:00</t>
+    <t>2026-02-13T12:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -667,7 +667,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/aps/r4/ValueSet/at-aps-immunization-vaccine-codes</t>
+    <t>https://termgit.elga.gv.at/ValueSet/at-aps-immunization-vaccine-codes</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1746,7 +1746,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="57.20703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="59.6171875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="56.7734375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-immunization.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-13T12:44:21+00:00</t>
+    <t>2026-02-16T08:31:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-immunization.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-immunization.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T08:31:54+00:00</t>
+    <t>2026-02-16T11:13:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-immunization.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T11:13:42+00:00</t>
+    <t>2026-02-17T09:00:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-immunization.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-immunization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2556" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2558" uniqueCount="453">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T09:00:43+00:00</t>
+    <t>2026-09-01T07:40:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -468,6 +468,11 @@
     <t>This extension implements the R5 basedOn element. A plan, order or recommendation fulfilled in whole or in part by this immunization.</t>
   </si>
   <si>
+    <t>Element `Immunization.basedOn` has a context of Immunization based on following the parent source element upwards and mapping to `Immunization`.
+Element `Immunization.basedOn` has no mapping targets in FHIR R4. Typically, this is because the element has been added (is a new element).
+Allows tracing of an authorization for the Immunization.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
@@ -537,10 +542,10 @@
 </t>
   </si>
   <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+    <t>A plan, order or recommendation fulfilled in whole or in part by this immunization.</t>
+  </si>
+  <si>
+    <t>Allows tracing of an authorization for the Immunization.</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -2854,7 +2859,9 @@
       <c r="M10" t="s" s="2">
         <v>145</v>
       </c>
-      <c r="N10" s="2"/>
+      <c r="N10" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>79</v>
@@ -2912,7 +2919,7 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>140</v>
@@ -2924,7 +2931,7 @@
         <v>79</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>132</v>
+        <v>79</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>79</v>
@@ -2935,10 +2942,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2961,13 +2968,13 @@
         <v>79</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -3018,7 +3025,7 @@
         <v>79</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3039,7 +3046,7 @@
         <v>79</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>79</v>
@@ -3050,10 +3057,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3124,7 +3131,7 @@
         <v>137</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>79</v>
@@ -3133,7 +3140,7 @@
         <v>138</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3165,10 +3172,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3194,13 +3201,13 @@
         <v>103</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3208,7 +3215,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>79</v>
@@ -3250,7 +3257,7 @@
         <v>79</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>89</v>
@@ -3282,10 +3289,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3308,15 +3315,17 @@
         <v>79</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="M14" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="N14" s="2"/>
+      <c r="N14" t="s" s="2">
+        <v>170</v>
+      </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>79</v>
@@ -3365,7 +3374,7 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3397,14 +3406,14 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3426,16 +3435,16 @@
         <v>134</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>79</v>
@@ -3484,7 +3493,7 @@
         <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3516,10 +3525,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3542,13 +3551,13 @@
         <v>79</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3599,7 +3608,7 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3614,27 +3623,27 @@
         <v>101</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3660,13 +3669,13 @@
         <v>109</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3692,13 +3701,13 @@
         <v>79</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>79</v>
@@ -3716,7 +3725,7 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>89</v>
@@ -3731,16 +3740,16 @@
         <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>79</v>
@@ -3748,10 +3757,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3774,16 +3783,16 @@
         <v>79</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3809,13 +3818,13 @@
         <v>79</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>79</v>
@@ -3833,7 +3842,7 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3848,13 +3857,13 @@
         <v>101</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>79</v>
@@ -3865,10 +3874,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3891,13 +3900,13 @@
         <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3924,11 +3933,11 @@
         <v>79</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>79</v>
@@ -3946,7 +3955,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>89</v>
@@ -3961,27 +3970,27 @@
         <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4004,13 +4013,13 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4061,7 +4070,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>89</v>
@@ -4076,16 +4085,16 @@
         <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>79</v>
@@ -4093,10 +4102,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4119,13 +4128,13 @@
         <v>79</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4176,7 +4185,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4191,16 +4200,16 @@
         <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>79</v>
@@ -4208,10 +4217,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4234,16 +4243,16 @@
         <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4293,7 +4302,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>89</v>
@@ -4308,27 +4317,27 @@
         <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4351,13 +4360,13 @@
         <v>79</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4408,7 +4417,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4429,10 +4438,10 @@
         <v>79</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>79</v>
@@ -4440,10 +4449,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4466,16 +4475,16 @@
         <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4525,7 +4534,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4543,13 +4552,13 @@
         <v>79</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>79</v>
@@ -4557,10 +4566,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4583,16 +4592,16 @@
         <v>79</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4618,13 +4627,13 @@
         <v>79</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>79</v>
@@ -4642,7 +4651,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4660,13 +4669,13 @@
         <v>79</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>79</v>
@@ -4674,10 +4683,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4700,13 +4709,13 @@
         <v>79</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4757,7 +4766,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4772,16 +4781,16 @@
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>79</v>
@@ -4789,10 +4798,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4815,13 +4824,13 @@
         <v>79</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4872,7 +4881,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4890,24 +4899,24 @@
         <v>79</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4930,13 +4939,13 @@
         <v>79</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4987,7 +4996,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5005,24 +5014,24 @@
         <v>79</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5045,13 +5054,13 @@
         <v>79</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5102,7 +5111,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5120,10 +5129,10 @@
         <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>79</v>
@@ -5134,10 +5143,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5160,13 +5169,13 @@
         <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5193,13 +5202,13 @@
         <v>79</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>79</v>
@@ -5217,7 +5226,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5235,24 +5244,24 @@
         <v>79</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5275,13 +5284,13 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5308,11 +5317,11 @@
         <v>79</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>79</v>
@@ -5330,7 +5339,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5348,24 +5357,24 @@
         <v>79</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5388,13 +5397,13 @@
         <v>79</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5445,7 +5454,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5463,10 +5472,10 @@
         <v>79</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>79</v>
@@ -5477,10 +5486,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5503,13 +5512,13 @@
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5560,7 +5569,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5575,13 +5584,13 @@
         <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>79</v>
@@ -5592,10 +5601,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5618,13 +5627,13 @@
         <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5675,7 +5684,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5696,7 +5705,7 @@
         <v>79</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>79</v>
@@ -5707,14 +5716,14 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5736,13 +5745,13 @@
         <v>134</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5792,7 +5801,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5813,7 +5822,7 @@
         <v>79</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>79</v>
@@ -5824,14 +5833,14 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5853,16 +5862,16 @@
         <v>134</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>79</v>
@@ -5911,7 +5920,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5943,10 +5952,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5969,13 +5978,13 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6002,13 +6011,13 @@
         <v>79</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>79</v>
@@ -6026,7 +6035,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6041,13 +6050,13 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>79</v>
@@ -6058,10 +6067,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6084,16 +6093,16 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6143,7 +6152,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>89</v>
@@ -6158,16 +6167,16 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>79</v>
@@ -6175,10 +6184,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6201,13 +6210,13 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6258,7 +6267,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6273,13 +6282,13 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>79</v>
@@ -6290,10 +6299,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6316,13 +6325,13 @@
         <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6349,13 +6358,13 @@
         <v>79</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>79</v>
@@ -6373,7 +6382,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6388,13 +6397,13 @@
         <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>79</v>
@@ -6405,10 +6414,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6431,13 +6440,13 @@
         <v>79</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6488,7 +6497,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6503,7 +6512,7 @@
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>79</v>
@@ -6520,10 +6529,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6546,23 +6555,23 @@
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q42" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="R42" t="s" s="2">
         <v>79</v>
@@ -6607,7 +6616,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6625,7 +6634,7 @@
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>132</v>
@@ -6639,10 +6648,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6665,13 +6674,13 @@
         <v>79</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6698,13 +6707,13 @@
         <v>79</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>79</v>
@@ -6722,7 +6731,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6754,10 +6763,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6780,13 +6789,13 @@
         <v>79</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6837,7 +6846,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6849,7 +6858,7 @@
         <v>79</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>79</v>
@@ -6869,10 +6878,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6895,13 +6904,13 @@
         <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6952,7 +6961,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -6973,7 +6982,7 @@
         <v>79</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>79</v>
@@ -6984,14 +6993,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7013,13 +7022,13 @@
         <v>134</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7069,7 +7078,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7090,7 +7099,7 @@
         <v>79</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>79</v>
@@ -7101,14 +7110,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7130,16 +7139,16 @@
         <v>134</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>79</v>
@@ -7188,7 +7197,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7220,10 +7229,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7246,13 +7255,13 @@
         <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7303,7 +7312,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7321,7 +7330,7 @@
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>132</v>
@@ -7335,10 +7344,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7364,10 +7373,10 @@
         <v>103</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7418,7 +7427,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7450,10 +7459,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7476,13 +7485,13 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7533,7 +7542,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7551,7 +7560,7 @@
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>132</v>
@@ -7565,10 +7574,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7591,13 +7600,13 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7648,7 +7657,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7666,7 +7675,7 @@
         <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>132</v>
@@ -7680,10 +7689,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7706,13 +7715,13 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7739,13 +7748,13 @@
         <v>79</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>79</v>
@@ -7763,7 +7772,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7781,7 +7790,7 @@
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>132</v>
@@ -7795,10 +7804,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7821,13 +7830,13 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7854,13 +7863,13 @@
         <v>79</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>79</v>
@@ -7878,7 +7887,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -7910,10 +7919,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7936,16 +7945,16 @@
         <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7995,7 +8004,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8013,10 +8022,10 @@
         <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>79</v>
@@ -8027,10 +8036,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8053,13 +8062,13 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8110,7 +8119,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8131,7 +8140,7 @@
         <v>79</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>79</v>
@@ -8142,14 +8151,14 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8171,13 +8180,13 @@
         <v>134</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8227,7 +8236,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8248,7 +8257,7 @@
         <v>79</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>79</v>
@@ -8259,14 +8268,14 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8288,16 +8297,16 @@
         <v>134</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>79</v>
@@ -8346,7 +8355,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8378,10 +8387,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8404,13 +8413,13 @@
         <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8461,7 +8470,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8479,10 +8488,10 @@
         <v>79</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>79</v>
@@ -8493,10 +8502,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8519,13 +8528,13 @@
         <v>79</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8576,7 +8585,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8594,10 +8603,10 @@
         <v>79</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>79</v>
@@ -8608,10 +8617,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8634,13 +8643,13 @@
         <v>79</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8691,7 +8700,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -8709,10 +8718,10 @@
         <v>79</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>79</v>
@@ -8723,10 +8732,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8749,13 +8758,13 @@
         <v>79</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8806,7 +8815,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -8838,10 +8847,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8864,13 +8873,13 @@
         <v>79</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8921,7 +8930,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -8942,7 +8951,7 @@
         <v>79</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>79</v>
@@ -8953,14 +8962,14 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -8982,13 +8991,13 @@
         <v>134</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9038,7 +9047,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9059,7 +9068,7 @@
         <v>79</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>79</v>
@@ -9070,14 +9079,14 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9099,16 +9108,16 @@
         <v>134</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>79</v>
@@ -9157,7 +9166,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9189,10 +9198,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9215,13 +9224,13 @@
         <v>79</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9272,7 +9281,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9304,10 +9313,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9330,13 +9339,13 @@
         <v>79</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9387,7 +9396,7 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9419,10 +9428,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9445,13 +9454,13 @@
         <v>79</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9478,11 +9487,11 @@
         <v>79</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Y67" s="2"/>
       <c r="Z67" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>79</v>
@@ -9500,7 +9509,7 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -9532,10 +9541,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9558,16 +9567,16 @@
         <v>79</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9617,7 +9626,7 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>89</v>
@@ -9649,10 +9658,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9675,16 +9684,16 @@
         <v>79</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9734,7 +9743,7 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
